--- a/excel/excel/Item.xlsx
+++ b/excel/excel/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tools\excel\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE3A708-E897-4842-AB57-33D07C7DA0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7C39EC-EFE3-4212-B205-F131C137377F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>id</t>
   </si>
@@ -463,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
@@ -575,7 +575,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -587,6 +587,26 @@
         <v>1</v>
       </c>
       <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1001</v>
+      </c>
+      <c r="B7">
+        <v>1001</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
     </row>

--- a/excel/excel/Item.xlsx
+++ b/excel/excel/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tools\excel\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7C39EC-EFE3-4212-B205-F131C137377F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99549948-8CAC-459A-BBFA-27BE1F4AE587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -584,7 +584,7 @@
         <v>16</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -604,7 +604,7 @@
         <v>16</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>1</v>
